--- a/Luban/Config/Datas/SceneInfo.xlsx
+++ b/Luban/Config/Datas/SceneInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21600" windowHeight="10730" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1476,6 +1476,11 @@
       </c>
       <c r="P4" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t>关卡 1：开阔棋盘：把路让给玩家自己塑造</t>
+        </is>
       </c>
     </row>
     <row r="5" s="1">
@@ -1484,7 +1489,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>6,7,8,9,10</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -1524,10 +1529,10 @@
         <v>2</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="M5" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N5" s="0" t="n">
         <v>3000</v>
@@ -1536,7 +1541,12 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0" t="inlineStr">
+        <is>
+          <t>关卡 2：双障碍夹出中段窄口</t>
+        </is>
       </c>
     </row>
     <row r="6" s="1">
@@ -1545,7 +1555,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>11,12,13,14,15</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -1585,10 +1595,10 @@
         <v>3</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="M6" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N6" s="0" t="n">
         <v>3000</v>
@@ -1597,7 +1607,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="0" t="inlineStr">
+        <is>
+          <t>关卡 3：厚横墙：好建位变少</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1607,7 +1622,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>16,17,18,19,20</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -1647,10 +1662,10 @@
         <v>4</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N7" s="0" t="n">
         <v>3000</v>
@@ -1659,7 +1674,12 @@
         <v>0</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="Q7" s="0" t="inlineStr">
+        <is>
+          <t>关卡 4：双交错横墙，S 形走位</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="1" s="2">
@@ -1669,7 +1689,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>21,22,23,24,25</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -1709,10 +1729,10 @@
         <v>5</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N8" s="8" t="n">
         <v>3000</v>
@@ -1721,7 +1741,12 @@
         <v>0</v>
       </c>
       <c r="P8" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="Q8" s="0" t="inlineStr">
+        <is>
+          <t>关卡 5：中央大块障碍，贴路可建位稀缺</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="1" s="2">
@@ -1731,7 +1756,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>26,27,28,29,30</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -1771,10 +1796,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N9" s="0" t="n">
         <v>3000</v>
@@ -1783,7 +1808,12 @@
         <v>0</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="Q9" s="0" t="inlineStr">
+        <is>
+          <t>关卡 6：井字街区，内侧位置差</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="1" s="2">
@@ -1793,7 +1823,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>31,32,33,34,35</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -1833,10 +1863,10 @@
         <v>7</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>100</v>
+        <v>1800</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N10" s="11" t="n">
         <v>3000</v>
@@ -1846,6 +1876,11 @@
       </c>
       <c r="P10" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q10" s="0" t="inlineStr">
+        <is>
+          <t>关卡 7：密集障碍，可建位少、容错低</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="2">
@@ -1855,7 +1890,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10</t>
+          <t>36,37,38,39,40</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -1895,10 +1930,10 @@
         <v>8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>100</v>
+        <v>2400</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>3000</v>
@@ -1908,6 +1943,11 @@
       </c>
       <c r="P11" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="Q11" s="0" t="inlineStr">
+        <is>
+          <t>关卡 8：终盘：障碍最密，可建位最少</t>
+        </is>
       </c>
     </row>
     <row r="12" s="1">

--- a/Luban/Config/Datas/SceneInfo.xlsx
+++ b/Luban/Config/Datas/SceneInfo.xlsx
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="22.6296296296296" customWidth="1" style="2" min="3" max="3"/>
@@ -2390,18 +2390,334 @@
       </c>
     </row>
     <row r="19">
-      <c r="H19" s="11" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>76,77,78,79,80</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>关卡 16</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3650</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>M16 新图：16×9，col8 竖墙 3 格把左右隔开，S 左中 → E 右中</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="H20" s="11" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>81,82,83,84,85</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>关卡 17</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3800</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>M17 新图：17×9，中央 3 格横墙，S 上中 → E 下中</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="10" t="n"/>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>86,87,88,89,90</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>关卡 18</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>18</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3950</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>M18 新图：16×9，col8 竖墙 3 格，S 右中 → E 左中（16 的镜像）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>91,92,93,94,95</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>关卡 19</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>19</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>M19 新图：16×9，左下角 3 格横墙，S 左上 → E 左下</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>96,97,98,99,100</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>关卡 20</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>20</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4250</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>M20 新图：16×9，S/E 两端各贴一格障碍，中间全开阔</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/SceneInfo.xlsx
+++ b/Luban/Config/Datas/SceneInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1446,7 +1446,7 @@
         <v>20</v>
       </c>
       <c r="N4" s="0" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O4" s="0" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>关卡 1：开阔棋盘：把路让给玩家自己塑造</t>
+          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>6,7,8,9,10</t>
+          <t>21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -1506,13 +1506,13 @@
         <v>2</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="M5" s="0" t="n">
         <v>20</v>
       </c>
       <c r="N5" s="0" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O5" s="0" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Q5" s="0" t="inlineStr">
         <is>
-          <t>关卡 2：双障碍夹出中段窄口</t>
+          <t>M2 16x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>11,12,13,14,15</t>
+          <t>41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -1572,13 +1572,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>380</v>
+        <v>136</v>
       </c>
       <c r="M6" s="0" t="n">
         <v>20</v>
       </c>
       <c r="N6" s="0" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O6" s="0" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Q6" s="0" t="inlineStr">
         <is>
-          <t>关卡 3：厚横墙：好建位变少</t>
+          <t>M3 17x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>16,17,18,19,20</t>
+          <t>61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -1639,23 +1639,23 @@
         <v>4</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>600</v>
+        <v>154</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N7" s="0" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="0" t="inlineStr">
         <is>
-          <t>关卡 4：双交错横墙，S 形走位</t>
+          <t>M4 16x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>21,22,23,24,25</t>
+          <t>81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -1706,13 +1706,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>900</v>
+        <v>172</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O8" s="0" t="n">
         <v>0</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Q8" s="0" t="inlineStr">
         <is>
-          <t>关卡 5：中央大块障碍，贴路可建位稀缺</t>
+          <t>M5 17x9; obstacles=0; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>26,27,28,29,30</t>
+          <t>101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -1773,13 +1773,13 @@
         <v>6</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>1300</v>
+        <v>190</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N9" s="0" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O9" s="0" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Q9" s="0" t="inlineStr">
         <is>
-          <t>关卡 6：井字街区，内侧位置差</t>
+          <t>M6 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>31,32,33,34,35</t>
+          <t>121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -1840,23 +1840,23 @@
         <v>7</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>1800</v>
+        <v>208</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="0" t="inlineStr">
         <is>
-          <t>关卡 7：密集障碍，可建位少、容错低</t>
+          <t>M7 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>36,37,38,39,40</t>
+          <t>141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -1907,23 +1907,23 @@
         <v>8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>2400</v>
+        <v>226</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="0" t="inlineStr">
         <is>
-          <t>关卡 8：终盘：障碍最密，可建位最少</t>
+          <t>M8 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>41,42,43,44,45</t>
+          <t>161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177,178,179,180</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -1973,13 +1973,13 @@
         <v>9</v>
       </c>
       <c r="L12" s="0" t="n">
-        <v>2600</v>
+        <v>244</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O12" s="0" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Q12" s="0" t="inlineStr">
         <is>
-          <t>M9 新图：16×9 全开阔，S 右下 → E 中部偏上</t>
+          <t>M9 16x9; obstacles=4; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>46,47,48,49,50</t>
+          <t>181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -2039,13 +2039,13 @@
         <v>10</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>2750</v>
+        <v>262</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O13" s="0" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Q13" s="0" t="inlineStr">
         <is>
-          <t>M10 新图：16×9 全开阔，S 左上 → E 中右</t>
+          <t>M10 16x9; obstacles=4; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>51,52,53,54,55</t>
+          <t>201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216,217,218,219,220</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -2105,13 +2105,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="0" t="n">
-        <v>2900</v>
+        <v>280</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>0</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="Q14" s="0" t="inlineStr">
         <is>
-          <t>M11 新图：16×9 全开阔，S 左上 → E 左下</t>
+          <t>M11 16x9; obstacles=0; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>56,57,58,59,60</t>
+          <t>221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -2171,13 +2171,13 @@
         <v>12</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>3050</v>
+        <v>298</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O15" s="0" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="Q15" s="0" t="inlineStr">
         <is>
-          <t>M12 新图：16×9 全开阔，S 左下 → E 左上</t>
+          <t>M12 16x9; obstacles=0; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>61,62,63,64,65</t>
+          <t>241,242,243,244,245,246,247,248,249,250,251,252,253,254,255,256,257,258,259,260</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -2237,23 +2237,23 @@
         <v>13</v>
       </c>
       <c r="L16" s="0" t="n">
-        <v>3200</v>
+        <v>316</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="0" t="inlineStr">
         <is>
-          <t>M13 新图：16×9 全开阔，S 右下 → E 右上</t>
+          <t>M13 16x9; obstacles=0; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>66,67,68,69,70</t>
+          <t>261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -2303,23 +2303,23 @@
         <v>14</v>
       </c>
       <c r="L17" s="0" t="n">
-        <v>3350</v>
+        <v>334</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="0" t="inlineStr">
         <is>
-          <t>M14 新图：17×9，中央 3 格横墙断开上下路</t>
+          <t>M14 17x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>71,72,73,74,75</t>
+          <t>281,282,283,284,285,286,287,288,289,290,291,292,293,294,295,296,297,298,299,300</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -2369,51 +2369,51 @@
         <v>15</v>
       </c>
       <c r="L18" s="0" t="n">
-        <v>3500</v>
+        <v>352</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="O18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="0" t="inlineStr">
         <is>
-          <t>M15 新图：16×9，S 与 E 之间隔一格竖墙（3 格）</t>
+          <t>M15 16x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>76,77,78,79,80</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>18,32,9</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>60,0.2,0</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>MapModel8</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>0,0,20</t>
         </is>
@@ -2423,63 +2423,63 @@
           <t>42.5,3.5,22</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>关卡 16</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="L19" t="n">
-        <v>3650</v>
+      <c r="L19" s="0" t="n">
+        <v>370</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O19" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>M16 新图：16×9，col8 竖墙 3 格把左右隔开，S 左中 → E 右中</t>
+      <c r="P19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="0" t="inlineStr">
+        <is>
+          <t>M16 16x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>81,82,83,84,85</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>321,322,323,324,325,326,327,328,329,330,331,332,333,334,335,336,337,338,339,340</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>18,32,9</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>60,0.2,0</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>MapModel8</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>0,0,20</t>
         </is>
@@ -2489,233 +2489,233 @@
           <t>42.5,3.5,22</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>关卡 17</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="L20" t="n">
-        <v>3800</v>
+      <c r="L20" s="0" t="n">
+        <v>388</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O20" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>M17 新图：17×9，中央 3 格横墙，S 上中 → E 下中</t>
+      <c r="P20" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="0" t="inlineStr">
+        <is>
+          <t>M17 17x9; obstacles=3; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>86,87,88,89,90</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>341,342,343,344,345,346,347,348,349,350,351,352,353,354,355,356,357,358,359,360</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>18,32,9</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>60,0.2,0</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>MapModel8</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>0,0,20</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>42.5,3.5,22</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>关卡 18</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="L21" t="n">
-        <v>3950</v>
+      <c r="L21" s="0" t="n">
+        <v>406</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O21" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>M18 新图：16×9，col8 竖墙 3 格，S 右中 → E 左中（16 的镜像）</t>
+      <c r="P21" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="0" t="inlineStr">
+        <is>
+          <t>M18 16x9; obstacles=3; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>91,92,93,94,95</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>361,362,363,364,365,366,367,368,369,370,371,372,373,374,375,376,377,378,379,380</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>18,32,9</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>60,0.2,0</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>MapModel8</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>0,0,20</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>42.5,3.5,22</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>关卡 19</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="L22" t="n">
-        <v>4100</v>
-      </c>
-      <c r="M22" t="n">
-        <v>12</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="L22" s="0" t="n">
+        <v>424</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O22" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>M19 新图：16×9，左下角 3 格横墙，S 左上 → E 左下</t>
+      <c r="P22" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="0" t="inlineStr">
+        <is>
+          <t>M19 16x9; obstacles=3; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>96,97,98,99,100</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>381,382,383,384,385,386,387,388,389,390,391,392,393,394,395,396,397,398,399,400</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>18,32,9</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>60,0.2,0</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>MapModel8</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>0,0,20</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>42.5,3.5,22</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>关卡 20</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="L23" t="n">
-        <v>4250</v>
-      </c>
-      <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="L23" s="0" t="n">
+        <v>442</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O23" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>M20 新图：16×9，S/E 两端各贴一格障碍，中间全开阔</t>
+      <c r="P23" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="0" t="inlineStr">
+        <is>
+          <t>M20 16x9; obstacles=2; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/SceneInfo.xlsx
+++ b/Luban/Config/Datas/SceneInfo.xlsx
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="22.6296296296296" customWidth="1" style="2" min="3" max="3"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,401,402,403,404,405</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="M4" s="0" t="n">
         <v>20</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
+          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40</t>
+          <t>21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,406,407,408,409,410</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -1506,7 +1506,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="M5" s="0" t="n">
         <v>20</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Q5" s="0" t="inlineStr">
         <is>
-          <t>M2 16x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
+          <t>M2 16x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60</t>
+          <t>41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,411,412,413,414,415</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -1572,7 +1572,7 @@
         <v>3</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="M6" s="0" t="n">
         <v>20</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Q6" s="0" t="inlineStr">
         <is>
-          <t>M3 17x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
+          <t>M3 17x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80</t>
+          <t>61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80,416,417,418,419,420</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -1639,7 +1639,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>20</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Q7" s="0" t="inlineStr">
         <is>
-          <t>M4 16x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 20 clearable waves</t>
+          <t>M4 16x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100</t>
+          <t>81,82,83,84,85,86,87,88,89,90,91,92,93,94,95,96,97,98,99,100,421,422,423,424,425</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -1706,7 +1706,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>20</v>
@@ -1718,11 +1718,11 @@
         <v>0</v>
       </c>
       <c r="P8" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="0" t="inlineStr">
         <is>
-          <t>M5 17x9; obstacles=0; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
+          <t>M5 17x9; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120</t>
+          <t>101,102,103,104,105,106,107,108,109,110,111,112,113,114,115,116,117,118,119,120,426,427,428,429,430</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -1773,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>20</v>
@@ -1785,11 +1785,11 @@
         <v>0</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="0" t="inlineStr">
         <is>
-          <t>M6 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
+          <t>M6 16x9; obstacles=4; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140</t>
+          <t>121,122,123,124,125,126,127,128,129,130,131,132,133,134,135,136,137,138,139,140,431,432,433,434,435</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -1840,7 +1840,7 @@
         <v>7</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>20</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Q10" s="0" t="inlineStr">
         <is>
-          <t>M7 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
+          <t>M7 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160</t>
+          <t>141,142,143,144,145,146,147,148,149,150,151,152,153,154,155,156,157,158,159,160,436,437,438,439,440</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -1907,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>20</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="Q11" s="0" t="inlineStr">
         <is>
-          <t>M8 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 20 clearable waves</t>
+          <t>M8 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177,178,179,180</t>
+          <t>161,162,163,164,165,166,167,168,169,170,171,172,173,174,175,176,177,178,179,180,441,442,443,444,445</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="L12" s="0" t="n">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="M12" s="10" t="n">
         <v>20</v>
@@ -1985,11 +1985,11 @@
         <v>0</v>
       </c>
       <c r="P12" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="0" t="inlineStr">
         <is>
-          <t>M9 16x9; obstacles=4; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
+          <t>M9 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200</t>
+          <t>181,182,183,184,185,186,187,188,189,190,191,192,193,194,195,196,197,198,199,200,446,447,448,449,450</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -2039,7 +2039,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>262</v>
+        <v>196</v>
       </c>
       <c r="M13" s="10" t="n">
         <v>20</v>
@@ -2051,11 +2051,11 @@
         <v>0</v>
       </c>
       <c r="P13" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="0" t="inlineStr">
         <is>
-          <t>M10 16x9; obstacles=4; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
+          <t>M10 16x9; obstacles=4; no-build=0; open-route building; stage=2; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216,217,218,219,220</t>
+          <t>201,202,203,204,205,206,207,208,209,210,211,212,213,214,215,216,217,218,219,220,451,452,453,454,455</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -2105,7 +2105,7 @@
         <v>11</v>
       </c>
       <c r="L14" s="0" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="M14" s="10" t="n">
         <v>20</v>
@@ -2117,11 +2117,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="0" t="inlineStr">
         <is>
-          <t>M11 16x9; obstacles=0; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
+          <t>M11 16x9; obstacles=0; no-build=0; open-route building; stage=2; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240</t>
+          <t>221,222,223,224,225,226,227,228,229,230,231,232,233,234,235,236,237,238,239,240,456,457,458,459,460</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -2171,7 +2171,7 @@
         <v>12</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>298</v>
+        <v>204</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>20</v>
@@ -2183,11 +2183,11 @@
         <v>0</v>
       </c>
       <c r="P15" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="0" t="inlineStr">
         <is>
-          <t>M12 16x9; obstacles=0; no-build=0; open-route building; stage=3; preset=中等; 20 clearable waves</t>
+          <t>M12 16x9; obstacles=0; no-build=0; open-route building; stage=2; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>241,242,243,244,245,246,247,248,249,250,251,252,253,254,255,256,257,258,259,260</t>
+          <t>241,242,243,244,245,246,247,248,249,250,251,252,253,254,255,256,257,258,259,260,461,462,463,464,465</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -2237,7 +2237,7 @@
         <v>13</v>
       </c>
       <c r="L16" s="0" t="n">
-        <v>316</v>
+        <v>208</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>20</v>
@@ -2249,11 +2249,11 @@
         <v>0</v>
       </c>
       <c r="P16" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="0" t="inlineStr">
         <is>
-          <t>M13 16x9; obstacles=0; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
+          <t>M13 16x9; obstacles=0; no-build=0; open-route building; stage=3; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280</t>
+          <t>261,262,263,264,265,266,267,268,269,270,271,272,273,274,275,276,277,278,279,280,466,467,468,469,470</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -2303,7 +2303,7 @@
         <v>14</v>
       </c>
       <c r="L17" s="0" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>20</v>
@@ -2315,11 +2315,11 @@
         <v>0</v>
       </c>
       <c r="P17" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="0" t="inlineStr">
         <is>
-          <t>M14 17x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
+          <t>M14 17x9; obstacles=3; no-build=0; open-route building; stage=3; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>281,282,283,284,285,286,287,288,289,290,291,292,293,294,295,296,297,298,299,300</t>
+          <t>281,282,283,284,285,286,287,288,289,290,291,292,293,294,295,296,297,298,299,300,471,472,473,474,475</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -2369,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="L18" s="0" t="n">
-        <v>352</v>
+        <v>216</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>20</v>
@@ -2381,11 +2381,11 @@
         <v>0</v>
       </c>
       <c r="P18" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="0" t="inlineStr">
         <is>
-          <t>M15 16x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
+          <t>M15 16x9; obstacles=3; no-build=0; open-route building; stage=3; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320</t>
+          <t>301,302,303,304,305,306,307,308,309,310,311,312,313,314,315,316,317,318,319,320,476,477,478,479,480</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -2435,7 +2435,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="0" t="n">
-        <v>370</v>
+        <v>220</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>20</v>
@@ -2447,11 +2447,11 @@
         <v>0</v>
       </c>
       <c r="P19" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="0" t="inlineStr">
         <is>
-          <t>M16 16x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 20 clearable waves</t>
+          <t>M16 16x9; obstacles=3; no-build=0; open-route building; stage=3; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>321,322,323,324,325,326,327,328,329,330,331,332,333,334,335,336,337,338,339,340</t>
+          <t>321,322,323,324,325,326,327,328,329,330,331,332,333,334,335,336,337,338,339,340,481,482,483,484,485</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -2501,7 +2501,7 @@
         <v>17</v>
       </c>
       <c r="L20" s="0" t="n">
-        <v>388</v>
+        <v>224</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>20</v>
@@ -2513,11 +2513,11 @@
         <v>0</v>
       </c>
       <c r="P20" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="0" t="inlineStr">
         <is>
-          <t>M17 17x9; obstacles=3; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
+          <t>M17 17x9; obstacles=3; no-build=0; open-route building; stage=3; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>341,342,343,344,345,346,347,348,349,350,351,352,353,354,355,356,357,358,359,360</t>
+          <t>341,342,343,344,345,346,347,348,349,350,351,352,353,354,355,356,357,358,359,360,486,487,488,489,490</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -2567,7 +2567,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>406</v>
+        <v>228</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>20</v>
@@ -2579,11 +2579,11 @@
         <v>0</v>
       </c>
       <c r="P21" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="0" t="inlineStr">
         <is>
-          <t>M18 16x9; obstacles=3; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
+          <t>M18 16x9; obstacles=3; no-build=0; open-route building; stage=3; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>361,362,363,364,365,366,367,368,369,370,371,372,373,374,375,376,377,378,379,380</t>
+          <t>361,362,363,364,365,366,367,368,369,370,371,372,373,374,375,376,377,378,379,380,491,492,493,494,495</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -2633,7 +2633,7 @@
         <v>19</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>424</v>
+        <v>232</v>
       </c>
       <c r="M22" s="0" t="n">
         <v>20</v>
@@ -2645,11 +2645,11 @@
         <v>0</v>
       </c>
       <c r="P22" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="0" t="inlineStr">
         <is>
-          <t>M19 16x9; obstacles=3; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
+          <t>M19 16x9; obstacles=3; no-build=0; open-route building; stage=4; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>381,382,383,384,385,386,387,388,389,390,391,392,393,394,395,396,397,398,399,400</t>
+          <t>381,382,383,384,385,386,387,388,389,390,391,392,393,394,395,396,397,398,399,400,496,497,498,499,500</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -2699,7 +2699,7 @@
         <v>20</v>
       </c>
       <c r="L23" s="0" t="n">
-        <v>442</v>
+        <v>236</v>
       </c>
       <c r="M23" s="0" t="n">
         <v>20</v>
@@ -2711,11 +2711,671 @@
         <v>0</v>
       </c>
       <c r="P23" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="0" t="inlineStr">
         <is>
-          <t>M20 16x9; obstacles=2; no-build=0; open-route building; stage=5; preset=中等; 20 clearable waves</t>
+          <t>M20 16x9; obstacles=2; no-build=0; open-route building; stage=4; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>501,502,503,504,505,506,507,508,509,510,511,512,513,514,515,516,517,518,519,520,521,522,523,524,525</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>Level 21</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="0" t="inlineStr">
+        <is>
+          <t>M21 17x9; obstacles=5; no-build=0; open-route building; stage=4; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>526,527,528,529,530,531,532,533,534,535,536,537,538,539,540,541,542,543,544,545,546,547,548,549,550</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>Level 22</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>244</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N25" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="0" t="inlineStr">
+        <is>
+          <t>M22 17x9; obstacles=4; no-build=0; open-route building; stage=4; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>551,552,553,554,555,556,557,558,559,560,561,562,563,564,565,566,567,568,569,570,571,572,573,574,575</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>Level 23</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>248</v>
+      </c>
+      <c r="M26" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N26" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="0" t="inlineStr">
+        <is>
+          <t>M23 17x9; obstacles=4; no-build=0; open-route building; stage=4; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>576,577,578,579,580,581,582,583,584,585,586,587,588,589,590,591,592,593,594,595,596,597,598,599,600</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>Level 24</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>252</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="0" t="inlineStr">
+        <is>
+          <t>M24 17x9; obstacles=5; no-build=0; open-route building; stage=4; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>601,602,603,604,605,606,607,608,609,610,611,612,613,614,615,616,617,618,619,620,621,622,623,624,625</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>Level 25</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <v>256</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N28" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" s="0" t="inlineStr">
+        <is>
+          <t>M25 17x9; obstacles=4; no-build=0; open-route building; stage=5; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>626,627,628,629,630,631,632,633,634,635,636,637,638,639,640,641,642,643,644,645,646,647,648,649,650</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t>Level 26</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="L29" s="0" t="n">
+        <v>260</v>
+      </c>
+      <c r="M29" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N29" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="0" t="inlineStr">
+        <is>
+          <t>M26 17x9; obstacles=5; no-build=0; open-route building; stage=5; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>651,652,653,654,655,656,657,658,659,660,661,662,663,664,665,666,667,668,669,670,671,672,673,674,675</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t>Level 27</t>
+        </is>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <v>264</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N30" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="0" t="inlineStr">
+        <is>
+          <t>M27 17x9; obstacles=4; no-build=0; open-route building; stage=5; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>676,677,678,679,680,681,682,683,684,685,686,687,688,689,690,691,692,693,694,695,696,697,698,699,700</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>Level 28</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>268</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N31" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="0" t="inlineStr">
+        <is>
+          <t>M28 17x9; obstacles=4; no-build=0; open-route building; stage=5; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>701,702,703,704,705,706,707,708,709,710,711,712,713,714,715,716,717,718,719,720,721,722,723,724,725</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>Level 29</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>272</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N32" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="0" t="inlineStr">
+        <is>
+          <t>M29 17x9; obstacles=4; no-build=0; open-route building; stage=5; preset=中等; 25 clearable waves</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>726,727,728,729,730,731,732,733,734,735,736,737,738,739,740,741,742,743,744,745,746,747,748,749,750</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>18,32,9</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>60,0.2,0</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>MapModel8</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>0,0,20</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>42.5,3.5,22</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>Level 30</t>
+        </is>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>276</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N33" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="0" t="inlineStr">
+        <is>
+          <t>M30 17x9; obstacles=4; no-build=0; open-route building; stage=5; preset=中等; 25 clearable waves</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/SceneInfo.xlsx
+++ b/Luban/Config/Datas/SceneInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>160</v>
+        <v>620</v>
       </c>
       <c r="M4" s="0" t="n">
         <v>20</v>
@@ -1506,7 +1506,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>164</v>
+        <v>624</v>
       </c>
       <c r="M5" s="0" t="n">
         <v>20</v>
@@ -1572,7 +1572,7 @@
         <v>3</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>168</v>
+        <v>848</v>
       </c>
       <c r="M6" s="0" t="n">
         <v>20</v>
@@ -1639,7 +1639,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>172</v>
+        <v>632</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>20</v>
@@ -1706,7 +1706,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>176</v>
+        <v>2060</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>20</v>
@@ -1773,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>180</v>
+        <v>864</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>20</v>
@@ -1840,7 +1840,7 @@
         <v>7</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>184</v>
+        <v>644</v>
       </c>
       <c r="M10" s="8" t="n">
         <v>20</v>
@@ -1907,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>188</v>
+        <v>875</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>20</v>
@@ -1973,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="L12" s="0" t="n">
-        <v>192</v>
+        <v>880</v>
       </c>
       <c r="M12" s="10" t="n">
         <v>20</v>
@@ -2039,7 +2039,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>196</v>
+        <v>656</v>
       </c>
       <c r="M13" s="10" t="n">
         <v>20</v>
@@ -2105,7 +2105,7 @@
         <v>11</v>
       </c>
       <c r="L14" s="0" t="n">
-        <v>200</v>
+        <v>891</v>
       </c>
       <c r="M14" s="10" t="n">
         <v>20</v>
@@ -2171,7 +2171,7 @@
         <v>12</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>204</v>
+        <v>664</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
         <v>13</v>
       </c>
       <c r="L16" s="0" t="n">
-        <v>208</v>
+        <v>668</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>20</v>
@@ -2303,7 +2303,7 @@
         <v>14</v>
       </c>
       <c r="L17" s="0" t="n">
-        <v>212</v>
+        <v>672</v>
       </c>
       <c r="M17" s="10" t="n">
         <v>20</v>
@@ -2369,7 +2369,7 @@
         <v>15</v>
       </c>
       <c r="L18" s="0" t="n">
-        <v>216</v>
+        <v>676</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>20</v>
@@ -2435,7 +2435,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="0" t="n">
-        <v>220</v>
+        <v>680</v>
       </c>
       <c r="M19" s="10" t="n">
         <v>20</v>
@@ -2501,7 +2501,7 @@
         <v>17</v>
       </c>
       <c r="L20" s="0" t="n">
-        <v>224</v>
+        <v>923</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>20</v>
@@ -2567,7 +2567,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>228</v>
+        <v>688</v>
       </c>
       <c r="M21" s="10" t="n">
         <v>20</v>
@@ -2633,7 +2633,7 @@
         <v>19</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>232</v>
+        <v>692</v>
       </c>
       <c r="M22" s="0" t="n">
         <v>20</v>
@@ -2699,7 +2699,7 @@
         <v>20</v>
       </c>
       <c r="L23" s="0" t="n">
-        <v>236</v>
+        <v>696</v>
       </c>
       <c r="M23" s="0" t="n">
         <v>20</v>
@@ -2765,7 +2765,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="0" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="M24" s="0" t="n">
         <v>20</v>
@@ -2831,7 +2831,7 @@
         <v>22</v>
       </c>
       <c r="L25" s="0" t="n">
-        <v>244</v>
+        <v>704</v>
       </c>
       <c r="M25" s="0" t="n">
         <v>20</v>
@@ -2897,7 +2897,7 @@
         <v>23</v>
       </c>
       <c r="L26" s="0" t="n">
-        <v>248</v>
+        <v>708</v>
       </c>
       <c r="M26" s="0" t="n">
         <v>20</v>
@@ -2963,7 +2963,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="0" t="n">
-        <v>252</v>
+        <v>961</v>
       </c>
       <c r="M27" s="0" t="n">
         <v>20</v>
@@ -3029,7 +3029,7 @@
         <v>25</v>
       </c>
       <c r="L28" s="0" t="n">
-        <v>256</v>
+        <v>716</v>
       </c>
       <c r="M28" s="0" t="n">
         <v>20</v>
@@ -3095,7 +3095,7 @@
         <v>26</v>
       </c>
       <c r="L29" s="0" t="n">
-        <v>260</v>
+        <v>1584</v>
       </c>
       <c r="M29" s="0" t="n">
         <v>20</v>
@@ -3161,7 +3161,7 @@
         <v>27</v>
       </c>
       <c r="L30" s="0" t="n">
-        <v>264</v>
+        <v>724</v>
       </c>
       <c r="M30" s="0" t="n">
         <v>20</v>
@@ -3227,7 +3227,7 @@
         <v>28</v>
       </c>
       <c r="L31" s="0" t="n">
-        <v>268</v>
+        <v>728</v>
       </c>
       <c r="M31" s="0" t="n">
         <v>20</v>
@@ -3293,7 +3293,7 @@
         <v>29</v>
       </c>
       <c r="L32" s="0" t="n">
-        <v>272</v>
+        <v>732</v>
       </c>
       <c r="M32" s="0" t="n">
         <v>20</v>
@@ -3359,7 +3359,7 @@
         <v>30</v>
       </c>
       <c r="L33" s="0" t="n">
-        <v>276</v>
+        <v>736</v>
       </c>
       <c r="M33" s="0" t="n">
         <v>20</v>

--- a/Luban/Config/Datas/SceneInfo.xlsx
+++ b/Luban/Config/Datas/SceneInfo.xlsx
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>620</v>
+        <v>230</v>
       </c>
       <c r="M4" s="0" t="n">
         <v>20</v>
